--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106849797</v>
       </c>
       <c r="B2" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>106849798</v>
       </c>
       <c r="B3" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106849797</v>
+        <v>135445400</v>
       </c>
       <c r="B2" t="n">
-        <v>103385</v>
+        <v>43472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -710,27 +710,32 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:44 (2), gräns mot plantage (före 1976), Gtl</t>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703426</v>
+        <v>703263</v>
       </c>
       <c r="R2" t="n">
-        <v>6360729</v>
+        <v>6360988</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,17 +759,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>5,2 m hög spenslig med 4 stammar (+ flera döda): 3 cm + 4 cm + 5 cm + 6 cm i diameter.</t>
+          <t>Slit et ex; slött.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +783,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog med rikligt av lundstarr och örnbräken.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,62 +801,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106849798</v>
+        <v>135445256</v>
       </c>
       <c r="B3" t="n">
-        <v>103385</v>
+        <v>104719</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6037533</v>
+        <v>220164</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:44 (2), Gtl</t>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703424</v>
+        <v>703434</v>
       </c>
       <c r="R3" t="n">
-        <v>6360716</v>
+        <v>6360991</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +861,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Hejde</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>6 m hög spenslig med 3 stammar: 1, 5 cm + 3 cm + 8 cm i diameter.</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,11 +882,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -914,6 +895,1296 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135445260</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104719</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>703455</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6360990</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalklbarrskog, på skogsväg.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135445222</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>703325</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6360794</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135445252</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>703412</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6360951</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135445255</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>703434</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6360991</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135445202</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>703258</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6360995</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135445240</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>703403</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6360866</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135445257</v>
+      </c>
+      <c r="B10" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>703434</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6360991</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalklbarrskog, på skogsväg.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135445261</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>703455</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6360990</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalklbarrskog, på skogsväg.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>106849797</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:44 (2), gräns mot plantage (före 1976), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>703426</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6360729</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5,2 m hög spenslig med 4 stammar (+ flera döda): 3 cm + 4 cm + 5 cm + 6 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>106849798</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:44 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>703424</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6360716</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>6 m hög spenslig med 3 stammar: 1, 5 cm + 3 cm + 8 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135445215</v>
+      </c>
+      <c r="B14" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>703352</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6360863</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 m hög. Stam 0,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135445245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>703415</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6360893</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 m hög. Stam 0,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445400</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445256</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445260</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445222</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445252</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445255</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445202</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445240</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445257</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1706,6 +1756,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445261</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106849797</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106849798</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2069,6 +2134,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445215</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,8 +2255,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135445400</v>
+        <v>135650734</v>
       </c>
       <c r="B2" t="n">
-        <v>43472</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -734,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703263</v>
+        <v>703325</v>
       </c>
       <c r="R2" t="n">
-        <v>6360988</v>
+        <v>6360794</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Slit et ex; slött.</t>
+          <t>Tall med gott om insektshål. Födosök (äldre) av spillkråka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +774,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog med rikligt av lundstarr och örnbräken.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,51 +791,56 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445400</t>
+          <t>https://artportalen.se/Sighting/135650734</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135445256</v>
+        <v>135650736</v>
       </c>
       <c r="B3" t="n">
-        <v>104719</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hejde Lojsthajd 1:1., Gtl</t>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703434</v>
+        <v>703416</v>
       </c>
       <c r="R3" t="n">
-        <v>6360991</v>
+        <v>6360911</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Hejde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,6 +875,11 @@
           <t>2026-07-06</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tall död stående med en del utgångshål för insekter. Födosök spiollkråka (äldre).</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +888,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -907,51 +908,56 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445256</t>
+          <t>https://artportalen.se/Sighting/135650736</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135445260</v>
+        <v>135650737</v>
       </c>
       <c r="B4" t="n">
-        <v>104719</v>
+        <v>57977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220164</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hejde Lojsthajd 1:1., Gtl</t>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703455</v>
+        <v>703396</v>
       </c>
       <c r="R4" t="n">
-        <v>6360990</v>
+        <v>6360903</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,7 +979,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Hejde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -986,6 +992,11 @@
           <t>2026-07-06</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tall död stående med en del utgångshål för insekter. Födosök spiollkråka (äldre).</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -997,7 +1008,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Kalklbarrskog, på skogsväg.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1014,16 +1025,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445260</t>
+          <t>https://artportalen.se/Sighting/135650737</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135445222</v>
+        <v>135445400</v>
       </c>
       <c r="B5" t="n">
-        <v>110159</v>
+        <v>43477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,37 +1042,56 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703325</v>
+        <v>703263</v>
       </c>
       <c r="R5" t="n">
-        <v>6360794</v>
+        <v>6360988</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,6 +1123,11 @@
           <t>2026-07-06</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Slit et ex; slött.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1104,7 +1139,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+          <t>Kalkbarrskog med rikligt av lundstarr och örnbräken.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1121,16 +1156,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445222</t>
+          <t>https://artportalen.se/Sighting/135445400</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135445252</v>
+        <v>135445256</v>
       </c>
       <c r="B6" t="n">
-        <v>110159</v>
+        <v>104773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,34 +1173,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703412</v>
+        <v>703434</v>
       </c>
       <c r="R6" t="n">
-        <v>6360951</v>
+        <v>6360991</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1187,7 +1222,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Hejde</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1208,11 +1243,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalktallskog, halvgammal, enstaka gran.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1228,16 +1258,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445252</t>
+          <t>https://artportalen.se/Sighting/135445256</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135445255</v>
+        <v>135445260</v>
       </c>
       <c r="B7" t="n">
-        <v>110159</v>
+        <v>104773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,21 +1275,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703434</v>
+        <v>703455</v>
       </c>
       <c r="R7" t="n">
-        <v>6360991</v>
+        <v>6360990</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1316,6 +1346,11 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalklbarrskog, på skogsväg.</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1330,33 +1365,33 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445255</t>
+          <t>https://artportalen.se/Sighting/135445260</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135445202</v>
+        <v>135445222</v>
       </c>
       <c r="B8" t="n">
-        <v>106894</v>
+        <v>110215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1371,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703258</v>
+        <v>703325</v>
       </c>
       <c r="R8" t="n">
-        <v>6360995</v>
+        <v>6360794</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,33 +1472,33 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445202</t>
+          <t>https://artportalen.se/Sighting/135445222</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135445240</v>
+        <v>135445252</v>
       </c>
       <c r="B9" t="n">
-        <v>106894</v>
+        <v>110215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1478,13 +1513,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703403</v>
+        <v>703412</v>
       </c>
       <c r="R9" t="n">
-        <v>6360866</v>
+        <v>6360951</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,16 +1579,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445240</t>
+          <t>https://artportalen.se/Sighting/135445252</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135445257</v>
+        <v>135445255</v>
       </c>
       <c r="B10" t="n">
-        <v>107598</v>
+        <v>110215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,16 +1596,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1632,11 +1667,6 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalklbarrskog, på skogsväg.</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
@@ -1651,33 +1681,33 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445257</t>
+          <t>https://artportalen.se/Sighting/135445255</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135445261</v>
+        <v>135445202</v>
       </c>
       <c r="B11" t="n">
-        <v>107598</v>
+        <v>106949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1688,17 +1718,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hejde Lojsthajd 1:1., Gtl</t>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703455</v>
+        <v>703258</v>
       </c>
       <c r="R11" t="n">
-        <v>6360990</v>
+        <v>6360995</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1717,7 +1747,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Hejde</t>
+          <t>Lojsta</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1741,7 +1771,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalklbarrskog, på skogsväg.</t>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1758,68 +1788,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445261</t>
+          <t>https://artportalen.se/Sighting/135445202</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106849797</v>
+        <v>135445240</v>
       </c>
       <c r="B12" t="n">
-        <v>103385</v>
+        <v>106949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:44 (2), gräns mot plantage (före 1976), Gtl</t>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703426</v>
+        <v>703403</v>
       </c>
       <c r="R12" t="n">
-        <v>6360729</v>
+        <v>6360866</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,17 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>5,2 m hög spenslig med 4 stammar (+ flera döda): 3 cm + 4 cm + 5 cm + 6 cm i diameter.</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,7 +1878,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1884,68 +1895,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106849797</t>
+          <t>https://artportalen.se/Sighting/135445240</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106849798</v>
+        <v>135445257</v>
       </c>
       <c r="B13" t="n">
-        <v>103385</v>
+        <v>107653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6037533</v>
+        <v>221849</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:44 (2), Gtl</t>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703424</v>
+        <v>703434</v>
       </c>
       <c r="R13" t="n">
-        <v>6360716</v>
+        <v>6360991</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,22 +1961,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Hejde</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>6 m hög spenslig med 3 stammar: 1, 5 cm + 3 cm + 8 cm i diameter.</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,7 +1985,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalklbarrskog, på skogsväg.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2010,68 +2002,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106849798</t>
+          <t>https://artportalen.se/Sighting/135445257</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135445215</v>
+        <v>135445261</v>
       </c>
       <c r="B14" t="n">
-        <v>103385</v>
+        <v>107653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6037533</v>
+        <v>221849</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703352</v>
+        <v>703455</v>
       </c>
       <c r="R14" t="n">
-        <v>6360863</v>
+        <v>6360990</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2090,7 +2068,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Lojsta</t>
+          <t>Hejde</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2103,11 +2081,6 @@
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 m hög. Stam 0,5 cm i diameter.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2119,7 +2092,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+          <t>Kalklbarrskog, på skogsväg.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2136,13 +2109,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135445215</t>
+          <t>https://artportalen.se/Sighting/135445261</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135445245</v>
+        <v>106849797</v>
       </c>
       <c r="B15" t="n">
         <v>103385</v>
@@ -2180,16 +2153,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+          <t>Lojsta, Bjärs 1:44 (2), gräns mot plantage (före 1976), Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703415</v>
+        <v>703426</v>
       </c>
       <c r="R15" t="n">
-        <v>6360893</v>
+        <v>6360729</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2216,17 +2194,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 m hög. Stam 0,5 cm i diameter.</t>
+          <t>5,2 m hög spenslig med 4 stammar (+ flera döda): 3 cm + 4 cm + 5 cm + 6 cm i diameter.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2240,7 +2218,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2257,7 +2235,501 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/106849797</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>106849798</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:44 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>703424</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6360716</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>6 m hög spenslig med 3 stammar: 1, 5 cm + 3 cm + 8 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106849798</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135445215</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103436</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>703352</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6360863</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 m hög. Stam 0,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445215</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135445245</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103436</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>703415</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6360893</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 m hög. Stam 0,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135445245</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135642140</v>
+      </c>
+      <c r="B19" t="n">
+        <v>103436</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Väg 142, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>703418</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6360888</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135642140</t>
         </is>
       </c>
     </row>
@@ -2277,6 +2749,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>135445256</v>
       </c>
       <c r="B6" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135445260</v>
       </c>
       <c r="B7" t="n">
-        <v>104773</v>
+        <v>104800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135445222</v>
       </c>
       <c r="B8" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135445252</v>
       </c>
       <c r="B9" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135445255</v>
       </c>
       <c r="B10" t="n">
-        <v>110215</v>
+        <v>110242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>135445202</v>
       </c>
       <c r="B11" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135445240</v>
       </c>
       <c r="B12" t="n">
-        <v>106949</v>
+        <v>106976</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135445257</v>
       </c>
       <c r="B13" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>135445261</v>
       </c>
       <c r="B14" t="n">
-        <v>107653</v>
+        <v>107680</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135445215</v>
       </c>
       <c r="B17" t="n">
-        <v>103436</v>
+        <v>103463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>135445245</v>
       </c>
       <c r="B18" t="n">
-        <v>103436</v>
+        <v>103463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135642140</v>
       </c>
       <c r="B19" t="n">
-        <v>103436</v>
+        <v>103463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,62 +680,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106849797</v>
+        <v>135650734</v>
       </c>
       <c r="B2" t="n">
-        <v>103385</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6037533</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:44 (2), gräns mot plantage (före 1976), Gtl</t>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703426</v>
+        <v>703325</v>
       </c>
       <c r="R2" t="n">
-        <v>6360729</v>
+        <v>6360794</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,17 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>5,2 m hög spenslig med 4 stammar (+ flera döda): 3 cm + 4 cm + 5 cm + 6 cm i diameter.</t>
+          <t>Tall med gott om insektshål. Födosök (äldre) av spillkråka.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,68 +791,59 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106849797</t>
+          <t>https://artportalen.se/Sighting/135650734</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106849798</v>
+        <v>135650736</v>
       </c>
       <c r="B3" t="n">
-        <v>103385</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6037533</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lojsta, Bjärs 1:44 (2), Gtl</t>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703424</v>
+        <v>703416</v>
       </c>
       <c r="R3" t="n">
-        <v>6360716</v>
+        <v>6360911</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,17 +867,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>6 m hög spenslig med 3 stammar: 1, 5 cm + 3 cm + 8 cm i diameter.</t>
+          <t>Tall död stående med en del utgångshål för insekter. Födosök spiollkråka (äldre).</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,7 +908,1828 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135650736</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135650737</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>703396</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6360903</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tall död stående med en del utgångshål för insekter. Födosök spiollkråka (äldre).</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135650737</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135445400</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43477</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>703263</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6360988</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Slit et ex; slött.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med rikligt av lundstarr och örnbräken.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445400</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135445256</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104805</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>703434</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6360991</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445256</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135445260</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104805</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>703455</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6360990</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalklbarrskog, på skogsväg.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445260</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135445222</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>703325</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6360794</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445222</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135445252</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>703412</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6360951</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445252</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135445255</v>
+      </c>
+      <c r="B10" t="n">
+        <v>110247</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>703434</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6360991</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445255</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135445202</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106981</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>703258</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6360995</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445202</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135445240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106981</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>703403</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6360866</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445240</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135445257</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>703434</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6360991</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalklbarrskog, på skogsväg.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445257</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135445261</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107685</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hejde Lojsthajd 1:1., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>703455</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6360990</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hejde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalklbarrskog, på skogsväg.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445261</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>106849797</v>
+      </c>
+      <c r="B15" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:44 (2), gräns mot plantage (före 1976), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>703426</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6360729</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5,2 m hög spenslig med 4 stammar (+ flera döda): 3 cm + 4 cm + 5 cm + 6 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106849797</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>106849798</v>
+      </c>
+      <c r="B16" t="n">
+        <v>103385</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lojsta, Bjärs 1:44 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>703424</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6360716</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>6 m hög spenslig med 3 stammar: 1, 5 cm + 3 cm + 8 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/106849798</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135445215</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103468</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>703352</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6360863</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1 m hög. Stam 0,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445215</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135445245</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103468</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lojsta Bjärs 1:44 (2) A 999-2023., Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>703415</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6360893</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 m hög. Stam 0,5 cm i diameter.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalktallskog, halvgammal, enstaka gran.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135445245</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135642140</v>
+      </c>
+      <c r="B19" t="n">
+        <v>103468</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Väg 142, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>703418</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6360888</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lojsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135642140</t>
         </is>
       </c>
     </row>
@@ -934,6 +2737,22 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>135445256</v>
       </c>
       <c r="B6" t="n">
-        <v>104805</v>
+        <v>104807</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135445260</v>
       </c>
       <c r="B7" t="n">
-        <v>104805</v>
+        <v>104807</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135445222</v>
       </c>
       <c r="B8" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135445252</v>
       </c>
       <c r="B9" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135445255</v>
       </c>
       <c r="B10" t="n">
-        <v>110247</v>
+        <v>110249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>135445202</v>
       </c>
       <c r="B11" t="n">
-        <v>106981</v>
+        <v>106983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135445240</v>
       </c>
       <c r="B12" t="n">
-        <v>106981</v>
+        <v>106983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135445257</v>
       </c>
       <c r="B13" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>135445261</v>
       </c>
       <c r="B14" t="n">
-        <v>107685</v>
+        <v>107687</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135445215</v>
       </c>
       <c r="B17" t="n">
-        <v>103468</v>
+        <v>103470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>135445245</v>
       </c>
       <c r="B18" t="n">
-        <v>103468</v>
+        <v>103470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135642140</v>
       </c>
       <c r="B19" t="n">
-        <v>103468</v>
+        <v>103470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135650734</v>
       </c>
       <c r="B2" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135650736</v>
       </c>
       <c r="B3" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135650737</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135445400</v>
       </c>
       <c r="B5" t="n">
-        <v>43477</v>
+        <v>43479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>135445256</v>
       </c>
       <c r="B6" t="n">
-        <v>104807</v>
+        <v>104827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>135445260</v>
       </c>
       <c r="B7" t="n">
-        <v>104807</v>
+        <v>104827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>135445222</v>
       </c>
       <c r="B8" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135445252</v>
       </c>
       <c r="B9" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>135445255</v>
       </c>
       <c r="B10" t="n">
-        <v>110249</v>
+        <v>110272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>135445202</v>
       </c>
       <c r="B11" t="n">
-        <v>106983</v>
+        <v>107003</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>135445240</v>
       </c>
       <c r="B12" t="n">
-        <v>106983</v>
+        <v>107003</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>135445257</v>
       </c>
       <c r="B13" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>135445261</v>
       </c>
       <c r="B14" t="n">
-        <v>107687</v>
+        <v>107710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
         <v>135445215</v>
       </c>
       <c r="B17" t="n">
-        <v>103470</v>
+        <v>103490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>135445245</v>
       </c>
       <c r="B18" t="n">
-        <v>103470</v>
+        <v>103490</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135642140</v>
       </c>
       <c r="B19" t="n">
-        <v>103470</v>
+        <v>103490</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -2617,7 +2617,7 @@
         <v>135642140</v>
       </c>
       <c r="B19" t="n">
-        <v>103490</v>
+        <v>103492</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -2617,7 +2617,7 @@
         <v>135642140</v>
       </c>
       <c r="B19" t="n">
-        <v>103492</v>
+        <v>103493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135650734</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135650736</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135650737</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135642140</v>
       </c>
       <c r="B19" t="n">
-        <v>103493</v>
+        <v>103494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135650734</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135650736</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135650737</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135642140</v>
       </c>
       <c r="B19" t="n">
-        <v>103494</v>
+        <v>103500</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 999-2023 artfynd.xlsx
+++ b/artfynd/A 999-2023 artfynd.xlsx
@@ -2617,7 +2617,7 @@
         <v>135642140</v>
       </c>
       <c r="B19" t="n">
-        <v>103500</v>
+        <v>103501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
